--- a/outputs/tables/tab-8-ame-por-area.xlsx
+++ b/outputs/tables/tab-8-ame-por-area.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,26 @@
           <t>ame</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ep</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sup</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -411,6 +431,18 @@
       <c r="F2">
         <v>-0.05249601263885482</v>
       </c>
+      <c r="G2">
+        <v>0.003570856076365567</v>
+      </c>
+      <c r="H2">
+        <v>-0.05949476194250734</v>
+      </c>
+      <c r="I2">
+        <v>-0.04549726333520231</v>
+      </c>
+      <c r="J2">
+        <v>6.32899292446941E-49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -437,6 +469,18 @@
       <c r="F3">
         <v>-0.008438660074986415</v>
       </c>
+      <c r="G3">
+        <v>0.005423705053097973</v>
+      </c>
+      <c r="H3">
+        <v>-0.01906892664182634</v>
+      </c>
+      <c r="I3">
+        <v>0.002191606491853512</v>
+      </c>
+      <c r="J3">
+        <v>0.1197354962032066</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -460,6 +504,18 @@
       <c r="F4">
         <v>-0.08112111593218381</v>
       </c>
+      <c r="G4">
+        <v>0.00851674709991144</v>
+      </c>
+      <c r="H4">
+        <v>-0.09781363351344619</v>
+      </c>
+      <c r="I4">
+        <v>-0.06442859835092143</v>
+      </c>
+      <c r="J4">
+        <v>1.652099579208806E-21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,6 +539,18 @@
       <c r="F5">
         <v>-0.03198898568134848</v>
       </c>
+      <c r="G5">
+        <v>0.01230587147229333</v>
+      </c>
+      <c r="H5">
+        <v>-0.0561080505654223</v>
+      </c>
+      <c r="I5">
+        <v>-0.007869920797274662</v>
+      </c>
+      <c r="J5">
+        <v>0.009336249043445913</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -506,6 +574,18 @@
       <c r="F6">
         <v>-0.01180990714630456</v>
       </c>
+      <c r="G6">
+        <v>0.01309991044864499</v>
+      </c>
+      <c r="H6">
+        <v>-0.03748525982634866</v>
+      </c>
+      <c r="I6">
+        <v>0.01386544553373955</v>
+      </c>
+      <c r="J6">
+        <v>0.3673088266129211</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -529,6 +609,18 @@
       <c r="F7">
         <v>-0.01801841805424372</v>
       </c>
+      <c r="G7">
+        <v>0.01320935598744997</v>
+      </c>
+      <c r="H7">
+        <v>-0.04390828004861418</v>
+      </c>
+      <c r="I7">
+        <v>0.007871443940126732</v>
+      </c>
+      <c r="J7">
+        <v>0.1725471596359555</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -555,6 +647,18 @@
       <c r="F8">
         <v>-0.01713423417253614</v>
       </c>
+      <c r="G8">
+        <v>0.004830865977551723</v>
+      </c>
+      <c r="H8">
+        <v>-0.0266025575026774</v>
+      </c>
+      <c r="I8">
+        <v>-0.007665910842394888</v>
+      </c>
+      <c r="J8">
+        <v>0.0003899041223776473</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -578,6 +682,18 @@
       <c r="F9">
         <v>-0.06148713057727676</v>
       </c>
+      <c r="G9">
+        <v>0.02280252687099946</v>
+      </c>
+      <c r="H9">
+        <v>-0.1061792620009425</v>
+      </c>
+      <c r="I9">
+        <v>-0.016794999153611</v>
+      </c>
+      <c r="J9">
+        <v>0.00700713192697863</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -601,6 +717,18 @@
       <c r="F10">
         <v>-0.03150238871190147</v>
       </c>
+      <c r="G10">
+        <v>0.01430522407531306</v>
+      </c>
+      <c r="H10">
+        <v>-0.05954011269029036</v>
+      </c>
+      <c r="I10">
+        <v>-0.003464664733512587</v>
+      </c>
+      <c r="J10">
+        <v>0.02765402591418346</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -624,6 +752,18 @@
       <c r="F11">
         <v>-0.04501744262503503</v>
       </c>
+      <c r="G11">
+        <v>0.0222246348789908</v>
+      </c>
+      <c r="H11">
+        <v>-0.0885769265574097</v>
+      </c>
+      <c r="I11">
+        <v>-0.001457958692660362</v>
+      </c>
+      <c r="J11">
+        <v>0.04280938087856366</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -647,6 +787,18 @@
       <c r="F12">
         <v>0.02110926807808764</v>
       </c>
+      <c r="G12">
+        <v>0.01097597732922284</v>
+      </c>
+      <c r="H12">
+        <v>-0.0004032521823172583</v>
+      </c>
+      <c r="I12">
+        <v>0.04262178833849255</v>
+      </c>
+      <c r="J12">
+        <v>0.0544518665939398</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -670,6 +822,18 @@
       <c r="F13">
         <v>-0.02179697721041132</v>
       </c>
+      <c r="G13">
+        <v>0.02134503244647082</v>
+      </c>
+      <c r="H13">
+        <v>-0.06363247205433299</v>
+      </c>
+      <c r="I13">
+        <v>0.02003851763351036</v>
+      </c>
+      <c r="J13">
+        <v>0.3071723401306529</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -693,6 +857,18 @@
       <c r="F14">
         <v>0.05715185798891124</v>
       </c>
+      <c r="G14">
+        <v>0.04763010569503588</v>
+      </c>
+      <c r="H14">
+        <v>-0.03620143375319518</v>
+      </c>
+      <c r="I14">
+        <v>0.1505051497310177</v>
+      </c>
+      <c r="J14">
+        <v>0.2301741501403776</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -716,6 +892,18 @@
       <c r="F15">
         <v>0.007271421625440979</v>
       </c>
+      <c r="G15">
+        <v>0.01081103751570807</v>
+      </c>
+      <c r="H15">
+        <v>-0.0139178225408582</v>
+      </c>
+      <c r="I15">
+        <v>0.02846066579174016</v>
+      </c>
+      <c r="J15">
+        <v>0.5012066406646476</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -742,6 +930,18 @@
       <c r="F16">
         <v>-0.01272311291213217</v>
       </c>
+      <c r="G16">
+        <v>0.004998533263149588</v>
+      </c>
+      <c r="H16">
+        <v>-0.02252005808343083</v>
+      </c>
+      <c r="I16">
+        <v>-0.002926167740833508</v>
+      </c>
+      <c r="J16">
+        <v>0.0109162233474308</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -768,6 +968,18 @@
       <c r="F17">
         <v>-0.02613337110854586</v>
       </c>
+      <c r="G17">
+        <v>0.009665745125173271</v>
+      </c>
+      <c r="H17">
+        <v>-0.04507788343762906</v>
+      </c>
+      <c r="I17">
+        <v>-0.007188858779462654</v>
+      </c>
+      <c r="J17">
+        <v>0.006857011804298765</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -794,6 +1006,18 @@
       <c r="F18">
         <v>-0.02567076940082567</v>
       </c>
+      <c r="G18">
+        <v>0.01326930121030233</v>
+      </c>
+      <c r="H18">
+        <v>-0.05167812187303198</v>
+      </c>
+      <c r="I18">
+        <v>0.0003365830713806389</v>
+      </c>
+      <c r="J18">
+        <v>0.05303959180747515</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -817,6 +1041,18 @@
       <c r="F19">
         <v>-0.01655607039048962</v>
       </c>
+      <c r="G19">
+        <v>0.02016895743801569</v>
+      </c>
+      <c r="H19">
+        <v>-0.05608650057472161</v>
+      </c>
+      <c r="I19">
+        <v>0.02297435979374237</v>
+      </c>
+      <c r="J19">
+        <v>0.4117209337951981</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -840,6 +1076,18 @@
       <c r="F20">
         <v>-0.02967957549844965</v>
       </c>
+      <c r="G20">
+        <v>0.02760062042715956</v>
+      </c>
+      <c r="H20">
+        <v>-0.08377579748664291</v>
+      </c>
+      <c r="I20">
+        <v>0.02441664648974361</v>
+      </c>
+      <c r="J20">
+        <v>0.2822302470488127</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -863,6 +1111,18 @@
       <c r="F21">
         <v>0.001253762179827883</v>
       </c>
+      <c r="G21">
+        <v>0.03595517943042294</v>
+      </c>
+      <c r="H21">
+        <v>-0.06921709456147644</v>
+      </c>
+      <c r="I21">
+        <v>0.0717246189211322</v>
+      </c>
+      <c r="J21">
+        <v>0.9721832900818757</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -886,6 +1146,18 @@
       <c r="F22">
         <v>-0.01800553251768778</v>
       </c>
+      <c r="G22">
+        <v>0.03515678098433547</v>
+      </c>
+      <c r="H22">
+        <v>-0.08691155705934793</v>
+      </c>
+      <c r="I22">
+        <v>0.05090049202397236</v>
+      </c>
+      <c r="J22">
+        <v>0.6085462894328018</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -912,6 +1184,18 @@
       <c r="F23">
         <v>-0.01063500344502827</v>
       </c>
+      <c r="G23">
+        <v>0.01152644411729214</v>
+      </c>
+      <c r="H23">
+        <v>-0.03322641878473442</v>
+      </c>
+      <c r="I23">
+        <v>0.01195641189467789</v>
+      </c>
+      <c r="J23">
+        <v>0.356183760724631</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -935,6 +1219,18 @@
       <c r="F24">
         <v>-0.02358682780292014</v>
       </c>
+      <c r="G24">
+        <v>0.06611198419470617</v>
+      </c>
+      <c r="H24">
+        <v>-0.1531639357710255</v>
+      </c>
+      <c r="I24">
+        <v>0.1059902801651852</v>
+      </c>
+      <c r="J24">
+        <v>0.7212633716311583</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -958,6 +1254,18 @@
       <c r="F25">
         <v>-0.001254887204226911</v>
       </c>
+      <c r="G25">
+        <v>0.03511415846330158</v>
+      </c>
+      <c r="H25">
+        <v>-0.07007737313973032</v>
+      </c>
+      <c r="I25">
+        <v>0.0675675987312765</v>
+      </c>
+      <c r="J25">
+        <v>0.9714917832722996</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -981,6 +1289,18 @@
       <c r="F26">
         <v>-0.01481173452616385</v>
       </c>
+      <c r="G26">
+        <v>0.05639976468594324</v>
+      </c>
+      <c r="H26">
+        <v>-0.1253532420471466</v>
+      </c>
+      <c r="I26">
+        <v>0.09572977299481886</v>
+      </c>
+      <c r="J26">
+        <v>0.7928430961222561</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1004,6 +1324,18 @@
       <c r="F27">
         <v>-0.003090105507031972</v>
       </c>
+      <c r="G27">
+        <v>0.02756347679612578</v>
+      </c>
+      <c r="H27">
+        <v>-0.05711352731614397</v>
+      </c>
+      <c r="I27">
+        <v>0.05093331630208002</v>
+      </c>
+      <c r="J27">
+        <v>0.9107372205805478</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1027,6 +1359,18 @@
       <c r="F28">
         <v>-0.05144900883340729</v>
       </c>
+      <c r="G28">
+        <v>0.0399366072921437</v>
+      </c>
+      <c r="H28">
+        <v>-0.1297233207907286</v>
+      </c>
+      <c r="I28">
+        <v>0.02682530312391403</v>
+      </c>
+      <c r="J28">
+        <v>0.1976530748910955</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1050,6 +1394,18 @@
       <c r="F29">
         <v>0.1170290996045661</v>
       </c>
+      <c r="G29">
+        <v>0.1363003400188897</v>
+      </c>
+      <c r="H29">
+        <v>-0.150114657913021</v>
+      </c>
+      <c r="I29">
+        <v>0.3841728571221532</v>
+      </c>
+      <c r="J29">
+        <v>0.3905546474943719</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1073,6 +1429,18 @@
       <c r="F30">
         <v>-0.1054478901841831</v>
       </c>
+      <c r="G30">
+        <v>0.02111308866124867</v>
+      </c>
+      <c r="H30">
+        <v>-0.1468287835626315</v>
+      </c>
+      <c r="I30">
+        <v>-0.06406699680573472</v>
+      </c>
+      <c r="J30">
+        <v>5.900911199129897E-07</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1097,7 +1465,19 @@
         <v>75.20368638939883</v>
       </c>
       <c r="F31">
-        <v>0.004742562561365315</v>
+        <v>0.004742562561365314</v>
+      </c>
+      <c r="G31">
+        <v>0.009915805602487587</v>
+      </c>
+      <c r="H31">
+        <v>-0.01469205929721084</v>
+      </c>
+      <c r="I31">
+        <v>0.02417718441994147</v>
+      </c>
+      <c r="J31">
+        <v>0.6324487003354535</v>
       </c>
     </row>
     <row r="32">
@@ -1125,6 +1505,18 @@
       <c r="F32">
         <v>-0.05637490573388894</v>
       </c>
+      <c r="G32">
+        <v>0.002819204292998597</v>
+      </c>
+      <c r="H32">
+        <v>-0.06190044461322689</v>
+      </c>
+      <c r="I32">
+        <v>-0.05084936685455099</v>
+      </c>
+      <c r="J32">
+        <v>5.878769438039915E-89</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1151,6 +1543,18 @@
       <c r="F33">
         <v>-0.02255260664853867</v>
       </c>
+      <c r="G33">
+        <v>0.004516792562645476</v>
+      </c>
+      <c r="H33">
+        <v>-0.03140535739696218</v>
+      </c>
+      <c r="I33">
+        <v>-0.01369985590011517</v>
+      </c>
+      <c r="J33">
+        <v>5.943074061397541E-07</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1174,6 +1578,18 @@
       <c r="F34">
         <v>-0.06801386477885474</v>
       </c>
+      <c r="G34">
+        <v>0.006853402659024917</v>
+      </c>
+      <c r="H34">
+        <v>-0.08144628716209461</v>
+      </c>
+      <c r="I34">
+        <v>-0.05458144239561486</v>
+      </c>
+      <c r="J34">
+        <v>3.270342213299852E-23</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1197,6 +1613,18 @@
       <c r="F35">
         <v>-0.02836967986961663</v>
       </c>
+      <c r="G35">
+        <v>0.008836995334049537</v>
+      </c>
+      <c r="H35">
+        <v>-0.04568987245590223</v>
+      </c>
+      <c r="I35">
+        <v>-0.01104948728333104</v>
+      </c>
+      <c r="J35">
+        <v>0.001325822153102566</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1218,7 +1646,19 @@
         </is>
       </c>
       <c r="F36">
-        <v>-0.0002935817761421908</v>
+        <v>-0.0002935817761421905</v>
+      </c>
+      <c r="G36">
+        <v>0.009906218394178011</v>
+      </c>
+      <c r="H36">
+        <v>-0.01970941305171929</v>
+      </c>
+      <c r="I36">
+        <v>0.01912224949943491</v>
+      </c>
+      <c r="J36">
+        <v>0.9763572664883666</v>
       </c>
     </row>
     <row r="37">
@@ -1243,6 +1683,18 @@
       <c r="F37">
         <v>-0.005468960131066182</v>
       </c>
+      <c r="G37">
+        <v>0.01010123666385528</v>
+      </c>
+      <c r="H37">
+        <v>-0.02526702019153804</v>
+      </c>
+      <c r="I37">
+        <v>0.01432909992940568</v>
+      </c>
+      <c r="J37">
+        <v>0.5882216331136458</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1269,6 +1721,18 @@
       <c r="F38">
         <v>-0.01012852948059167</v>
       </c>
+      <c r="G38">
+        <v>0.003809675193731216</v>
+      </c>
+      <c r="H38">
+        <v>-0.0175953556531005</v>
+      </c>
+      <c r="I38">
+        <v>-0.002661703308082835</v>
+      </c>
+      <c r="J38">
+        <v>0.007845829747928568</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1292,6 +1756,18 @@
       <c r="F39">
         <v>-0.04560851773784306</v>
       </c>
+      <c r="G39">
+        <v>0.02031544320822894</v>
+      </c>
+      <c r="H39">
+        <v>-0.08542605475594062</v>
+      </c>
+      <c r="I39">
+        <v>-0.005790980719745493</v>
+      </c>
+      <c r="J39">
+        <v>0.02476703374361359</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1315,6 +1791,18 @@
       <c r="F40">
         <v>-0.04485377025213959</v>
       </c>
+      <c r="G40">
+        <v>0.01135128672882424</v>
+      </c>
+      <c r="H40">
+        <v>-0.06710188341882257</v>
+      </c>
+      <c r="I40">
+        <v>-0.0226056570854566</v>
+      </c>
+      <c r="J40">
+        <v>7.768687380880689E-05</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1338,6 +1826,18 @@
       <c r="F41">
         <v>-0.06627223801529346</v>
       </c>
+      <c r="G41">
+        <v>0.01782605174331134</v>
+      </c>
+      <c r="H41">
+        <v>-0.1012106574187311</v>
+      </c>
+      <c r="I41">
+        <v>-0.0313338186118558</v>
+      </c>
+      <c r="J41">
+        <v>0.0002010302871267104</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1359,7 +1859,19 @@
         </is>
       </c>
       <c r="F42">
-        <v>0.0001583734556118975</v>
+        <v>0.0001583734556118973</v>
+      </c>
+      <c r="G42">
+        <v>0.008572169726994948</v>
+      </c>
+      <c r="H42">
+        <v>-0.01664277047866274</v>
+      </c>
+      <c r="I42">
+        <v>0.01695951738988654</v>
+      </c>
+      <c r="J42">
+        <v>0.9852596774564684</v>
       </c>
     </row>
     <row r="43">
@@ -1384,6 +1896,18 @@
       <c r="F43">
         <v>-0.04466498236615204</v>
       </c>
+      <c r="G43">
+        <v>0.01508870289574557</v>
+      </c>
+      <c r="H43">
+        <v>-0.07423829661523856</v>
+      </c>
+      <c r="I43">
+        <v>-0.01509166811706551</v>
+      </c>
+      <c r="J43">
+        <v>0.003074788045164923</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1407,6 +1931,18 @@
       <c r="F44">
         <v>-0.04691736953416185</v>
       </c>
+      <c r="G44">
+        <v>0.0286739373201019</v>
+      </c>
+      <c r="H44">
+        <v>-0.1031172539765205</v>
+      </c>
+      <c r="I44">
+        <v>0.009282514908196822</v>
+      </c>
+      <c r="J44">
+        <v>0.1017899053799234</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1430,6 +1966,18 @@
       <c r="F45">
         <v>-0.01615919134653379</v>
       </c>
+      <c r="G45">
+        <v>0.008343885388744844</v>
+      </c>
+      <c r="H45">
+        <v>-0.03251290619960367</v>
+      </c>
+      <c r="I45">
+        <v>0.0001945235065360928</v>
+      </c>
+      <c r="J45">
+        <v>0.05278805789043626</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1454,7 +2002,19 @@
         <v>58.4586596460579</v>
       </c>
       <c r="F46">
-        <v>-0.005914440587151767</v>
+        <v>-0.005914440587151766</v>
+      </c>
+      <c r="G46">
+        <v>0.00360993560704924</v>
+      </c>
+      <c r="H46">
+        <v>-0.01298978436347701</v>
+      </c>
+      <c r="I46">
+        <v>0.001160903189173479</v>
+      </c>
+      <c r="J46">
+        <v>0.1013427785085421</v>
       </c>
     </row>
     <row r="47">
@@ -1482,6 +2042,18 @@
       <c r="F47">
         <v>-0.02204348205864473</v>
       </c>
+      <c r="G47">
+        <v>0.002061226517062904</v>
+      </c>
+      <c r="H47">
+        <v>-0.02608341179606695</v>
+      </c>
+      <c r="I47">
+        <v>-0.0180035523212225</v>
+      </c>
+      <c r="J47">
+        <v>1.081730431558939E-26</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1508,6 +2080,18 @@
       <c r="F48">
         <v>-0.03755084051439588</v>
       </c>
+      <c r="G48">
+        <v>0.004230622323659497</v>
+      </c>
+      <c r="H48">
+        <v>-0.04584270790095965</v>
+      </c>
+      <c r="I48">
+        <v>-0.02925897312783211</v>
+      </c>
+      <c r="J48">
+        <v>6.933187730295841E-19</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1531,6 +2115,18 @@
       <c r="F49">
         <v>-0.02499259563864163</v>
       </c>
+      <c r="G49">
+        <v>0.005606813173255084</v>
+      </c>
+      <c r="H49">
+        <v>-0.03598174752626633</v>
+      </c>
+      <c r="I49">
+        <v>-0.01400344375101694</v>
+      </c>
+      <c r="J49">
+        <v>8.290545699737033E-06</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1554,6 +2150,18 @@
       <c r="F50">
         <v>-0.01743801942194196</v>
       </c>
+      <c r="G50">
+        <v>0.006164260074187628</v>
+      </c>
+      <c r="H50">
+        <v>-0.02951974715868791</v>
+      </c>
+      <c r="I50">
+        <v>-0.005356291685196014</v>
+      </c>
+      <c r="J50">
+        <v>0.004670961465187889</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1577,6 +2185,18 @@
       <c r="F51">
         <v>0.00819387695866172</v>
       </c>
+      <c r="G51">
+        <v>0.007052994807984327</v>
+      </c>
+      <c r="H51">
+        <v>-0.005629738848135552</v>
+      </c>
+      <c r="I51">
+        <v>0.02201749276545899</v>
+      </c>
+      <c r="J51">
+        <v>0.245333558923701</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1600,6 +2220,18 @@
       <c r="F52">
         <v>0.01736282273041838</v>
       </c>
+      <c r="G52">
+        <v>0.007250748397840162</v>
+      </c>
+      <c r="H52">
+        <v>0.003151617009690164</v>
+      </c>
+      <c r="I52">
+        <v>0.0315740284511466</v>
+      </c>
+      <c r="J52">
+        <v>0.01663737543692967</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1626,6 +2258,18 @@
       <c r="F53">
         <v>-0.003854100371275537</v>
       </c>
+      <c r="G53">
+        <v>0.003107075588073826</v>
+      </c>
+      <c r="H53">
+        <v>-0.009943856621143842</v>
+      </c>
+      <c r="I53">
+        <v>0.002235655878592769</v>
+      </c>
+      <c r="J53">
+        <v>0.2148175089453718</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1649,6 +2293,18 @@
       <c r="F54">
         <v>-0.03794335191195136</v>
       </c>
+      <c r="G54">
+        <v>0.01040821138254651</v>
+      </c>
+      <c r="H54">
+        <v>-0.05834307136522236</v>
+      </c>
+      <c r="I54">
+        <v>-0.01754363245868036</v>
+      </c>
+      <c r="J54">
+        <v>0.0002668507467353871</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1672,6 +2328,18 @@
       <c r="F55">
         <v>-0.01488899108624516</v>
       </c>
+      <c r="G55">
+        <v>0.007537336251734555</v>
+      </c>
+      <c r="H55">
+        <v>-0.02966189867901301</v>
+      </c>
+      <c r="I55">
+        <v>-0.0001160834934773071</v>
+      </c>
+      <c r="J55">
+        <v>0.04822672874960465</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1695,6 +2363,18 @@
       <c r="F56">
         <v>-0.03155623976412256</v>
       </c>
+      <c r="G56">
+        <v>0.009488858936304389</v>
+      </c>
+      <c r="H56">
+        <v>-0.0501540615336602</v>
+      </c>
+      <c r="I56">
+        <v>-0.01295841799458491</v>
+      </c>
+      <c r="J56">
+        <v>0.0008822542675161513</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1718,6 +2398,18 @@
       <c r="F57">
         <v>0.02132501664721445</v>
       </c>
+      <c r="G57">
+        <v>0.00669152441684286</v>
+      </c>
+      <c r="H57">
+        <v>0.008209869788532064</v>
+      </c>
+      <c r="I57">
+        <v>0.03444016350589685</v>
+      </c>
+      <c r="J57">
+        <v>0.001438215337105042</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1741,6 +2433,18 @@
       <c r="F58">
         <v>-0.0034502334889794</v>
       </c>
+      <c r="G58">
+        <v>0.00981188210640469</v>
+      </c>
+      <c r="H58">
+        <v>-0.02268116903808559</v>
+      </c>
+      <c r="I58">
+        <v>0.01578070206012679</v>
+      </c>
+      <c r="J58">
+        <v>0.7251095422975147</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1764,6 +2468,18 @@
       <c r="F59">
         <v>-0.01237660943645688</v>
       </c>
+      <c r="G59">
+        <v>0.01912771728252564</v>
+      </c>
+      <c r="H59">
+        <v>-0.04986624641667148</v>
+      </c>
+      <c r="I59">
+        <v>0.02511302754375772</v>
+      </c>
+      <c r="J59">
+        <v>0.5175989082285248</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1787,6 +2503,18 @@
       <c r="F60">
         <v>-0.04653013761274406</v>
       </c>
+      <c r="G60">
+        <v>0.005243499374717833</v>
+      </c>
+      <c r="H60">
+        <v>-0.0568072075401493</v>
+      </c>
+      <c r="I60">
+        <v>-0.03625306768533881</v>
+      </c>
+      <c r="J60">
+        <v>7.064631808036656E-19</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1813,6 +2541,18 @@
       <c r="F61">
         <v>-0.01736638973440398</v>
       </c>
+      <c r="G61">
+        <v>0.002572842394288855</v>
+      </c>
+      <c r="H61">
+        <v>-0.02240906816510794</v>
+      </c>
+      <c r="I61">
+        <v>-0.01232371130370002</v>
+      </c>
+      <c r="J61">
+        <v>1.479626026940243E-11</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1839,6 +2579,18 @@
       <c r="F62">
         <v>-0.0196434922335402</v>
       </c>
+      <c r="G62">
+        <v>0.001960149990331198</v>
+      </c>
+      <c r="H62">
+        <v>-0.02348531561888588</v>
+      </c>
+      <c r="I62">
+        <v>-0.01580166884819451</v>
+      </c>
+      <c r="J62">
+        <v>1.227230762678559E-23</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1865,6 +2617,18 @@
       <c r="F63">
         <v>-0.03410530763107463</v>
       </c>
+      <c r="G63">
+        <v>0.003120298722140637</v>
+      </c>
+      <c r="H63">
+        <v>-0.04022098074747663</v>
+      </c>
+      <c r="I63">
+        <v>-0.02798963451467263</v>
+      </c>
+      <c r="J63">
+        <v>8.271902127997406E-28</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1886,7 +2650,19 @@
         </is>
       </c>
       <c r="F64">
-        <v>-0.0005178046253487246</v>
+        <v>-0.0005178046253487245</v>
+      </c>
+      <c r="G64">
+        <v>0.004408592468236859</v>
+      </c>
+      <c r="H64">
+        <v>-0.009158487085607509</v>
+      </c>
+      <c r="I64">
+        <v>0.00812287783491006</v>
+      </c>
+      <c r="J64">
+        <v>0.9065006887658316</v>
       </c>
     </row>
     <row r="65">
@@ -1911,6 +2687,18 @@
       <c r="F65">
         <v>-0.01222209938588316</v>
       </c>
+      <c r="G65">
+        <v>0.005206466238740104</v>
+      </c>
+      <c r="H65">
+        <v>-0.02242658570053748</v>
+      </c>
+      <c r="I65">
+        <v>-0.002017613071228837</v>
+      </c>
+      <c r="J65">
+        <v>0.01890065378354417</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1934,6 +2722,18 @@
       <c r="F66">
         <v>-0.000590444234855973</v>
       </c>
+      <c r="G66">
+        <v>0.006058038765000268</v>
+      </c>
+      <c r="H66">
+        <v>-0.012463982031204</v>
+      </c>
+      <c r="I66">
+        <v>0.01128309356149206</v>
+      </c>
+      <c r="J66">
+        <v>0.9223574572777751</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1957,6 +2757,18 @@
       <c r="F67">
         <v>0.005512364665576292</v>
       </c>
+      <c r="G67">
+        <v>0.006280397273133647</v>
+      </c>
+      <c r="H67">
+        <v>-0.006796987798369217</v>
+      </c>
+      <c r="I67">
+        <v>0.0178217171295218</v>
+      </c>
+      <c r="J67">
+        <v>0.3801013604527473</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1983,6 +2795,18 @@
       <c r="F68">
         <v>-0.01177651277002273</v>
       </c>
+      <c r="G68">
+        <v>0.002908162727219794</v>
+      </c>
+      <c r="H68">
+        <v>-0.01747640697655531</v>
+      </c>
+      <c r="I68">
+        <v>-0.006076618563490158</v>
+      </c>
+      <c r="J68">
+        <v>5.133413087570823E-05</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2006,6 +2830,18 @@
       <c r="F69">
         <v>-0.02634692494670538</v>
       </c>
+      <c r="G69">
+        <v>0.007500549133412882</v>
+      </c>
+      <c r="H69">
+        <v>-0.04104773111246773</v>
+      </c>
+      <c r="I69">
+        <v>-0.01164611878094302</v>
+      </c>
+      <c r="J69">
+        <v>0.0004436345507009742</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2027,7 +2863,19 @@
         </is>
       </c>
       <c r="F70">
-        <v>0.0002643727058949062</v>
+        <v>0.0002643727058949064</v>
+      </c>
+      <c r="G70">
+        <v>0.005885780485512131</v>
+      </c>
+      <c r="H70">
+        <v>-0.01127154506661754</v>
+      </c>
+      <c r="I70">
+        <v>0.01180029047840735</v>
+      </c>
+      <c r="J70">
+        <v>0.964173316993985</v>
       </c>
     </row>
     <row r="71">
@@ -2052,6 +2900,18 @@
       <c r="F71">
         <v>-0.0298362814647107</v>
       </c>
+      <c r="G71">
+        <v>0.006893575369646944</v>
+      </c>
+      <c r="H71">
+        <v>-0.04334744091393109</v>
+      </c>
+      <c r="I71">
+        <v>-0.0163251220154903</v>
+      </c>
+      <c r="J71">
+        <v>1.503815843463236E-05</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2075,6 +2935,18 @@
       <c r="F72">
         <v>0.02570529473901443</v>
       </c>
+      <c r="G72">
+        <v>0.006863301073030697</v>
+      </c>
+      <c r="H72">
+        <v>0.01225347182081916</v>
+      </c>
+      <c r="I72">
+        <v>0.0391571176572097</v>
+      </c>
+      <c r="J72">
+        <v>0.0001801602234403778</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2098,6 +2970,18 @@
       <c r="F73">
         <v>-0.02772634950073912</v>
       </c>
+      <c r="G73">
+        <v>0.006585894918150002</v>
+      </c>
+      <c r="H73">
+        <v>-0.04063446634627849</v>
+      </c>
+      <c r="I73">
+        <v>-0.01481823265519975</v>
+      </c>
+      <c r="J73">
+        <v>2.554167062439887E-05</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2121,6 +3005,18 @@
       <c r="F74">
         <v>0.008991059374399703</v>
       </c>
+      <c r="G74">
+        <v>0.02141014092730075</v>
+      </c>
+      <c r="H74">
+        <v>-0.03297204574703676</v>
+      </c>
+      <c r="I74">
+        <v>0.05095416449583616</v>
+      </c>
+      <c r="J74">
+        <v>0.6745263925036387</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2144,6 +3040,18 @@
       <c r="F75">
         <v>-0.03444730220832249</v>
       </c>
+      <c r="G75">
+        <v>0.004630164281493873</v>
+      </c>
+      <c r="H75">
+        <v>-0.04352225744255426</v>
+      </c>
+      <c r="I75">
+        <v>-0.02537234697409072</v>
+      </c>
+      <c r="J75">
+        <v>1.008698395190085E-13</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2170,6 +3078,18 @@
       <c r="F76">
         <v>-0.01326381781106824</v>
       </c>
+      <c r="G76">
+        <v>0.002214133011166223</v>
+      </c>
+      <c r="H76">
+        <v>-0.01760343876993525</v>
+      </c>
+      <c r="I76">
+        <v>-0.00892419685220122</v>
+      </c>
+      <c r="J76">
+        <v>2.091654997310135E-09</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2196,6 +3116,18 @@
       <c r="F77">
         <v>-0.01615870228331093</v>
       </c>
+      <c r="G77">
+        <v>0.001696756181344699</v>
+      </c>
+      <c r="H77">
+        <v>-0.01948428328929225</v>
+      </c>
+      <c r="I77">
+        <v>-0.01283312127732961</v>
+      </c>
+      <c r="J77">
+        <v>1.677802852154414E-21</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2222,6 +3154,18 @@
       <c r="F78">
         <v>-0.01997856467472248</v>
       </c>
+      <c r="G78">
+        <v>0.003296715689352176</v>
+      </c>
+      <c r="H78">
+        <v>-0.02644000869312088</v>
+      </c>
+      <c r="I78">
+        <v>-0.01351712065632408</v>
+      </c>
+      <c r="J78">
+        <v>1.360015667655236E-09</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2245,6 +3189,18 @@
       <c r="F79">
         <v>-0.03129743055533195</v>
       </c>
+      <c r="G79">
+        <v>0.004129070109933077</v>
+      </c>
+      <c r="H79">
+        <v>-0.03939025926044162</v>
+      </c>
+      <c r="I79">
+        <v>-0.02320460185022228</v>
+      </c>
+      <c r="J79">
+        <v>3.46149469394647E-14</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2268,6 +3224,18 @@
       <c r="F80">
         <v>-0.002805374910787127</v>
       </c>
+      <c r="G80">
+        <v>0.005698855420183975</v>
+      </c>
+      <c r="H80">
+        <v>-0.01397492628744859</v>
+      </c>
+      <c r="I80">
+        <v>0.00836417646587434</v>
+      </c>
+      <c r="J80">
+        <v>0.6225285653049247</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2291,6 +3259,18 @@
       <c r="F81">
         <v>-0.005978061198979568</v>
       </c>
+      <c r="G81">
+        <v>0.007439059758046543</v>
+      </c>
+      <c r="H81">
+        <v>-0.02055835040359204</v>
+      </c>
+      <c r="I81">
+        <v>0.0086022280056329</v>
+      </c>
+      <c r="J81">
+        <v>0.4216254776524515</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2314,6 +3294,18 @@
       <c r="F82">
         <v>-0.004998577217781864</v>
       </c>
+      <c r="G82">
+        <v>0.007343569961519411</v>
+      </c>
+      <c r="H82">
+        <v>-0.0193917098603101</v>
+      </c>
+      <c r="I82">
+        <v>0.009394555424746369</v>
+      </c>
+      <c r="J82">
+        <v>0.4960777847782675</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2340,6 +3332,18 @@
       <c r="F83">
         <v>-0.00575590862317121</v>
       </c>
+      <c r="G83">
+        <v>0.002458876820196948</v>
+      </c>
+      <c r="H83">
+        <v>-0.0105752186331776</v>
+      </c>
+      <c r="I83">
+        <v>-0.000936598613164823</v>
+      </c>
+      <c r="J83">
+        <v>0.01923891418252092</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2363,6 +3367,18 @@
       <c r="F84">
         <v>-0.02012903337133582</v>
       </c>
+      <c r="G84">
+        <v>0.01023711049905702</v>
+      </c>
+      <c r="H84">
+        <v>-0.04019340125524444</v>
+      </c>
+      <c r="I84">
+        <v>-6.466548742719777E-05</v>
+      </c>
+      <c r="J84">
+        <v>0.04926618850024341</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2386,6 +3402,18 @@
       <c r="F85">
         <v>-0.006190124473153315</v>
       </c>
+      <c r="G85">
+        <v>0.006929330639293768</v>
+      </c>
+      <c r="H85">
+        <v>-0.01977136296313901</v>
+      </c>
+      <c r="I85">
+        <v>0.007391114016832376</v>
+      </c>
+      <c r="J85">
+        <v>0.3716846850408191</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2409,6 +3437,18 @@
       <c r="F86">
         <v>-0.01398679183869788</v>
       </c>
+      <c r="G86">
+        <v>0.008895738992892168</v>
+      </c>
+      <c r="H86">
+        <v>-0.03142211988063513</v>
+      </c>
+      <c r="I86">
+        <v>0.003448536203239379</v>
+      </c>
+      <c r="J86">
+        <v>0.11588043488344</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2432,6 +3472,18 @@
       <c r="F87">
         <v>0.02190352415237344</v>
       </c>
+      <c r="G87">
+        <v>0.007216300242199793</v>
+      </c>
+      <c r="H87">
+        <v>0.007759835576034177</v>
+      </c>
+      <c r="I87">
+        <v>0.0360472127287127</v>
+      </c>
+      <c r="J87">
+        <v>0.002403089003404512</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2455,6 +3507,18 @@
       <c r="F88">
         <v>-0.009544515420328269</v>
       </c>
+      <c r="G88">
+        <v>0.007304272634991848</v>
+      </c>
+      <c r="H88">
+        <v>-0.02386062671817377</v>
+      </c>
+      <c r="I88">
+        <v>0.004771595877517231</v>
+      </c>
+      <c r="J88">
+        <v>0.1913135782402846</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2478,6 +3542,18 @@
       <c r="F89">
         <v>0.05123106942405657</v>
       </c>
+      <c r="G89">
+        <v>0.03091353171712576</v>
+      </c>
+      <c r="H89">
+        <v>-0.009358339376446548</v>
+      </c>
+      <c r="I89">
+        <v>0.1118204782245597</v>
+      </c>
+      <c r="J89">
+        <v>0.09747143236632565</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2501,6 +3577,18 @@
       <c r="F90">
         <v>-0.02887269869654392</v>
       </c>
+      <c r="G90">
+        <v>0.004192645261959344</v>
+      </c>
+      <c r="H90">
+        <v>-0.03709013240993674</v>
+      </c>
+      <c r="I90">
+        <v>-0.02065526498315111</v>
+      </c>
+      <c r="J90">
+        <v>5.717724720785327E-12</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2527,6 +3615,18 @@
       <c r="F91">
         <v>-0.02128996562091138</v>
       </c>
+      <c r="G91">
+        <v>0.002083995657610159</v>
+      </c>
+      <c r="H91">
+        <v>-0.02537452205376516</v>
+      </c>
+      <c r="I91">
+        <v>-0.01720540918805761</v>
+      </c>
+      <c r="J91">
+        <v>1.682479596282573E-24</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2553,6 +3653,18 @@
       <c r="F92">
         <v>-0.0259562220425292</v>
       </c>
+      <c r="G92">
+        <v>0.002272428333525628</v>
+      </c>
+      <c r="H92">
+        <v>-0.0304100997336878</v>
+      </c>
+      <c r="I92">
+        <v>-0.0215023443513706</v>
+      </c>
+      <c r="J92">
+        <v>3.237791532845628E-30</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2579,6 +3691,18 @@
       <c r="F93">
         <v>-0.01838949603233435</v>
       </c>
+      <c r="G93">
+        <v>0.003542124021677484</v>
+      </c>
+      <c r="H93">
+        <v>-0.02533193154359639</v>
+      </c>
+      <c r="I93">
+        <v>-0.01144706052107231</v>
+      </c>
+      <c r="J93">
+        <v>2.084297544262115E-07</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2602,6 +3726,18 @@
       <c r="F94">
         <v>-0.03795647162238487</v>
       </c>
+      <c r="G94">
+        <v>0.006581243348052206</v>
+      </c>
+      <c r="H94">
+        <v>-0.050855471558061</v>
+      </c>
+      <c r="I94">
+        <v>-0.02505747168670875</v>
+      </c>
+      <c r="J94">
+        <v>8.051770228433716E-09</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2625,6 +3761,18 @@
       <c r="F95">
         <v>-0.01959596531921282</v>
       </c>
+      <c r="G95">
+        <v>0.007288383739218103</v>
+      </c>
+      <c r="H95">
+        <v>-0.03388093495358767</v>
+      </c>
+      <c r="I95">
+        <v>-0.00531099568483797</v>
+      </c>
+      <c r="J95">
+        <v>0.007174005125527974</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2648,6 +3796,18 @@
       <c r="F96">
         <v>-0.006939222240278418</v>
       </c>
+      <c r="G96">
+        <v>0.01054714459241368</v>
+      </c>
+      <c r="H96">
+        <v>-0.02761124578114561</v>
+      </c>
+      <c r="I96">
+        <v>0.01373280130058878</v>
+      </c>
+      <c r="J96">
+        <v>0.5105868046234279</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2671,6 +3831,18 @@
       <c r="F97">
         <v>-0.02351977727874872</v>
       </c>
+      <c r="G97">
+        <v>0.01029390254479215</v>
+      </c>
+      <c r="H97">
+        <v>-0.04369545552690654</v>
+      </c>
+      <c r="I97">
+        <v>-0.003344099030590904</v>
+      </c>
+      <c r="J97">
+        <v>0.02232302619388525</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2697,6 +3869,18 @@
       <c r="F98">
         <v>-0.003576676868556902</v>
       </c>
+      <c r="G98">
+        <v>0.003193645054300975</v>
+      </c>
+      <c r="H98">
+        <v>-0.009836106154391277</v>
+      </c>
+      <c r="I98">
+        <v>0.002682752417277473</v>
+      </c>
+      <c r="J98">
+        <v>0.2627411959085188</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2720,6 +3904,18 @@
       <c r="F99">
         <v>-0.008520776179177562</v>
       </c>
+      <c r="G99">
+        <v>0.02132345142524686</v>
+      </c>
+      <c r="H99">
+        <v>-0.05031397299875067</v>
+      </c>
+      <c r="I99">
+        <v>0.03327242064039555</v>
+      </c>
+      <c r="J99">
+        <v>0.6894537478274505</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2743,6 +3939,18 @@
       <c r="F100">
         <v>-0.01440420263697163</v>
       </c>
+      <c r="G100">
+        <v>0.01058823087753153</v>
+      </c>
+      <c r="H100">
+        <v>-0.03515675381692836</v>
+      </c>
+      <c r="I100">
+        <v>0.006348348542985103</v>
+      </c>
+      <c r="J100">
+        <v>0.1737041745080149</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2766,6 +3974,18 @@
       <c r="F101">
         <v>-0.01391412363446225</v>
       </c>
+      <c r="G101">
+        <v>0.01796647478707862</v>
+      </c>
+      <c r="H101">
+        <v>-0.04912776714628329</v>
+      </c>
+      <c r="I101">
+        <v>0.02129951987735878</v>
+      </c>
+      <c r="J101">
+        <v>0.4386651453386221</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2789,6 +4009,18 @@
       <c r="F102">
         <v>0.01942132383162267</v>
       </c>
+      <c r="G102">
+        <v>0.008106882085475735</v>
+      </c>
+      <c r="H102">
+        <v>0.003532126917177268</v>
+      </c>
+      <c r="I102">
+        <v>0.03531052074606807</v>
+      </c>
+      <c r="J102">
+        <v>0.01659052358359774</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2810,7 +4042,19 @@
         </is>
       </c>
       <c r="F103">
-        <v>-0.005226838968905468</v>
+        <v>-0.005226838968905469</v>
+      </c>
+      <c r="G103">
+        <v>0.01470866824619356</v>
+      </c>
+      <c r="H103">
+        <v>-0.03405529899199276</v>
+      </c>
+      <c r="I103">
+        <v>0.02360162105418182</v>
+      </c>
+      <c r="J103">
+        <v>0.7223216110670376</v>
       </c>
     </row>
     <row r="104">
@@ -2835,6 +4079,18 @@
       <c r="F104">
         <v>-0.01494717585452895</v>
       </c>
+      <c r="G104">
+        <v>0.02750825734737241</v>
+      </c>
+      <c r="H104">
+        <v>-0.06886236953283818</v>
+      </c>
+      <c r="I104">
+        <v>0.03896801782378029</v>
+      </c>
+      <c r="J104">
+        <v>0.5868747250513828</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2858,6 +4114,18 @@
       <c r="F105">
         <v>-0.03094729233867041</v>
       </c>
+      <c r="G105">
+        <v>0.008398555516076543</v>
+      </c>
+      <c r="H105">
+        <v>-0.04740815867234064</v>
+      </c>
+      <c r="I105">
+        <v>-0.01448642600500018</v>
+      </c>
+      <c r="J105">
+        <v>0.000228850736539906</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2884,6 +4152,18 @@
       <c r="F106">
         <v>-0.01463566065678646</v>
       </c>
+      <c r="G106">
+        <v>0.002953200269108647</v>
+      </c>
+      <c r="H106">
+        <v>-0.0204238268233734</v>
+      </c>
+      <c r="I106">
+        <v>-0.008847494490199517</v>
+      </c>
+      <c r="J106">
+        <v>7.200935317624325E-07</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2910,6 +4190,18 @@
       <c r="F107">
         <v>-0.01455330744332888</v>
       </c>
+      <c r="G107">
+        <v>0.003403745998191728</v>
+      </c>
+      <c r="H107">
+        <v>-0.021224527012307</v>
+      </c>
+      <c r="I107">
+        <v>-0.007882087874350758</v>
+      </c>
+      <c r="J107">
+        <v>1.905601069911852E-05</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2936,6 +4228,18 @@
       <c r="F108">
         <v>-0.004049639002122844</v>
       </c>
+      <c r="G108">
+        <v>0.005274341465584284</v>
+      </c>
+      <c r="H108">
+        <v>-0.01438715831683424</v>
+      </c>
+      <c r="I108">
+        <v>0.006287880312588555</v>
+      </c>
+      <c r="J108">
+        <v>0.4426060567907223</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2959,6 +4263,18 @@
       <c r="F109">
         <v>-0.006160367930279289</v>
       </c>
+      <c r="G109">
+        <v>0.008085175817050812</v>
+      </c>
+      <c r="H109">
+        <v>-0.02200702134037309</v>
+      </c>
+      <c r="I109">
+        <v>0.009686285479814505</v>
+      </c>
+      <c r="J109">
+        <v>0.4460995750114213</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2982,6 +4298,18 @@
       <c r="F110">
         <v>-0.0008923310858167519</v>
       </c>
+      <c r="G110">
+        <v>0.01013849121394111</v>
+      </c>
+      <c r="H110">
+        <v>-0.0207634087227171</v>
+      </c>
+      <c r="I110">
+        <v>0.0189787465510836</v>
+      </c>
+      <c r="J110">
+        <v>0.9298653984087555</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3005,6 +4333,18 @@
       <c r="F111">
         <v>-0.009693515672500635</v>
       </c>
+      <c r="G111">
+        <v>0.01351228142541746</v>
+      </c>
+      <c r="H111">
+        <v>-0.03617710061528839</v>
+      </c>
+      <c r="I111">
+        <v>0.01679006927028712</v>
+      </c>
+      <c r="J111">
+        <v>0.4731362226870521</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3028,6 +4368,18 @@
       <c r="F112">
         <v>-0.01866823307400289</v>
       </c>
+      <c r="G112">
+        <v>0.01337928028811304</v>
+      </c>
+      <c r="H112">
+        <v>-0.04489114057777112</v>
+      </c>
+      <c r="I112">
+        <v>0.007554674429765335</v>
+      </c>
+      <c r="J112">
+        <v>0.1629226144824077</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3052,7 +4404,19 @@
         <v>2.167266123592437</v>
       </c>
       <c r="F113">
-        <v>2.517067518941864E-05</v>
+        <v>2.517067518941835E-05</v>
+      </c>
+      <c r="G113">
+        <v>0.004647692131635755</v>
+      </c>
+      <c r="H113">
+        <v>-0.009084138514046852</v>
+      </c>
+      <c r="I113">
+        <v>0.009134479864425688</v>
+      </c>
+      <c r="J113">
+        <v>0.995678888709549</v>
       </c>
     </row>
     <row r="114">
@@ -3077,6 +4441,18 @@
       <c r="F114">
         <v>0.001857235224927294</v>
       </c>
+      <c r="G114">
+        <v>0.01773223499463331</v>
+      </c>
+      <c r="H114">
+        <v>-0.03289730672995478</v>
+      </c>
+      <c r="I114">
+        <v>0.03661177717980936</v>
+      </c>
+      <c r="J114">
+        <v>0.9165838694153132</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3100,6 +4476,18 @@
       <c r="F115">
         <v>0.0166087990498627</v>
       </c>
+      <c r="G115">
+        <v>0.01070380468307918</v>
+      </c>
+      <c r="H115">
+        <v>-0.004370272626523661</v>
+      </c>
+      <c r="I115">
+        <v>0.03758787072624906</v>
+      </c>
+      <c r="J115">
+        <v>0.1207406131700468</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3123,6 +4511,18 @@
       <c r="F116">
         <v>-0.02788611763484555</v>
       </c>
+      <c r="G116">
+        <v>0.01227279475246721</v>
+      </c>
+      <c r="H116">
+        <v>-0.05194035333933345</v>
+      </c>
+      <c r="I116">
+        <v>-0.003831881930357654</v>
+      </c>
+      <c r="J116">
+        <v>0.0230750560604975</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3146,6 +4546,18 @@
       <c r="F117">
         <v>0.01411891631147324</v>
       </c>
+      <c r="G117">
+        <v>0.01279424265013677</v>
+      </c>
+      <c r="H117">
+        <v>-0.01095733849226113</v>
+      </c>
+      <c r="I117">
+        <v>0.03919517111520761</v>
+      </c>
+      <c r="J117">
+        <v>0.2697941631234822</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3169,6 +4581,18 @@
       <c r="F118">
         <v>-0.009512006355293793</v>
       </c>
+      <c r="G118">
+        <v>0.01273831911442144</v>
+      </c>
+      <c r="H118">
+        <v>-0.03447865304313796</v>
+      </c>
+      <c r="I118">
+        <v>0.01545464033255038</v>
+      </c>
+      <c r="J118">
+        <v>0.4552302860599594</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3192,6 +4616,18 @@
       <c r="F119">
         <v>-0.02186911571287718</v>
       </c>
+      <c r="G119">
+        <v>0.03647207368781059</v>
+      </c>
+      <c r="H119">
+        <v>-0.09335306658247686</v>
+      </c>
+      <c r="I119">
+        <v>0.04961483515672251</v>
+      </c>
+      <c r="J119">
+        <v>0.5487644336400488</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3215,6 +4651,18 @@
       <c r="F120">
         <v>-0.0340484431077006</v>
       </c>
+      <c r="G120">
+        <v>0.007956213700103878</v>
+      </c>
+      <c r="H120">
+        <v>-0.04964233541320835</v>
+      </c>
+      <c r="I120">
+        <v>-0.01845455080219284</v>
+      </c>
+      <c r="J120">
+        <v>1.873319821326626E-05</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3239,7 +4687,19 @@
         <v>38.06251542674941</v>
       </c>
       <c r="F121">
-        <v>0.001310321872134504</v>
+        <v>0.001310321872134503</v>
+      </c>
+      <c r="G121">
+        <v>0.003181430539050312</v>
+      </c>
+      <c r="H121">
+        <v>-0.004925167403719956</v>
+      </c>
+      <c r="I121">
+        <v>0.007545811147988963</v>
+      </c>
+      <c r="J121">
+        <v>0.6804379187384291</v>
       </c>
     </row>
     <row r="122">
@@ -3267,6 +4727,18 @@
       <c r="F122">
         <v>-0.01896824317401646</v>
       </c>
+      <c r="G122">
+        <v>0.001688717890185095</v>
+      </c>
+      <c r="H122">
+        <v>-0.02227806941882771</v>
+      </c>
+      <c r="I122">
+        <v>-0.01565841692920521</v>
+      </c>
+      <c r="J122">
+        <v>2.829054886349799E-29</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3293,6 +4765,18 @@
       <c r="F123">
         <v>-0.02448623665755528</v>
       </c>
+      <c r="G123">
+        <v>0.003162906958870899</v>
+      </c>
+      <c r="H123">
+        <v>-0.03068542038339335</v>
+      </c>
+      <c r="I123">
+        <v>-0.01828705293171721</v>
+      </c>
+      <c r="J123">
+        <v>9.810603014694257E-15</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3316,6 +4800,18 @@
       <c r="F124">
         <v>-0.006362017055564611</v>
       </c>
+      <c r="G124">
+        <v>0.004172389251430791</v>
+      </c>
+      <c r="H124">
+        <v>-0.014539749717851</v>
+      </c>
+      <c r="I124">
+        <v>0.001815715606721774</v>
+      </c>
+      <c r="J124">
+        <v>0.1273115059341134</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3339,6 +4835,18 @@
       <c r="F125">
         <v>-0.01587944156925608</v>
       </c>
+      <c r="G125">
+        <v>0.004784253352333639</v>
+      </c>
+      <c r="H125">
+        <v>-0.02525640583274504</v>
+      </c>
+      <c r="I125">
+        <v>-0.006502477305767135</v>
+      </c>
+      <c r="J125">
+        <v>0.0009030630737678313</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3362,6 +4870,18 @@
       <c r="F126">
         <v>-0.01093557056143131</v>
       </c>
+      <c r="G126">
+        <v>0.00580148831934596</v>
+      </c>
+      <c r="H126">
+        <v>-0.0223062787240792</v>
+      </c>
+      <c r="I126">
+        <v>0.0004351376012165752</v>
+      </c>
+      <c r="J126">
+        <v>0.05943530501951805</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3385,6 +4905,18 @@
       <c r="F127">
         <v>-0.006286026410454074</v>
       </c>
+      <c r="G127">
+        <v>0.006191558345734476</v>
+      </c>
+      <c r="H127">
+        <v>-0.01842125777627204</v>
+      </c>
+      <c r="I127">
+        <v>0.005849204955363892</v>
+      </c>
+      <c r="J127">
+        <v>0.3099830697467587</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3409,7 +4941,19 @@
         <v>1.702513328330893</v>
       </c>
       <c r="F128">
-        <v>0.0009048260759756424</v>
+        <v>0.0009048260759756425</v>
+      </c>
+      <c r="G128">
+        <v>0.002353246730167873</v>
+      </c>
+      <c r="H128">
+        <v>-0.003707452761890035</v>
+      </c>
+      <c r="I128">
+        <v>0.00551710491384132</v>
+      </c>
+      <c r="J128">
+        <v>0.7006070430846234</v>
       </c>
     </row>
     <row r="129">
@@ -3434,6 +4978,18 @@
       <c r="F129">
         <v>-0.04095463370435627</v>
       </c>
+      <c r="G129">
+        <v>0.006967383502658818</v>
+      </c>
+      <c r="H129">
+        <v>-0.05461045443604608</v>
+      </c>
+      <c r="I129">
+        <v>-0.02729881297266646</v>
+      </c>
+      <c r="J129">
+        <v>4.151257050125991E-09</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3457,6 +5013,18 @@
       <c r="F130">
         <v>-0.01292652147779368</v>
       </c>
+      <c r="G130">
+        <v>0.00593580123339223</v>
+      </c>
+      <c r="H130">
+        <v>-0.02456047811463088</v>
+      </c>
+      <c r="I130">
+        <v>-0.001292564840956478</v>
+      </c>
+      <c r="J130">
+        <v>0.02942678336914037</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3480,6 +5048,18 @@
       <c r="F131">
         <v>-0.01769065195265215</v>
       </c>
+      <c r="G131">
+        <v>0.008033444005756871</v>
+      </c>
+      <c r="H131">
+        <v>-0.03343591287575479</v>
+      </c>
+      <c r="I131">
+        <v>-0.001945391029549499</v>
+      </c>
+      <c r="J131">
+        <v>0.02765644419949469</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3503,6 +5083,18 @@
       <c r="F132">
         <v>0.01823861626684391</v>
       </c>
+      <c r="G132">
+        <v>0.005540129809992182</v>
+      </c>
+      <c r="H132">
+        <v>0.007380161369582503</v>
+      </c>
+      <c r="I132">
+        <v>0.02909707116410532</v>
+      </c>
+      <c r="J132">
+        <v>0.0009944512300774162</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3526,6 +5118,18 @@
       <c r="F133">
         <v>-0.01412109405301625</v>
       </c>
+      <c r="G133">
+        <v>0.006566149894699471</v>
+      </c>
+      <c r="H133">
+        <v>-0.02699051136371868</v>
+      </c>
+      <c r="I133">
+        <v>-0.001251676742313825</v>
+      </c>
+      <c r="J133">
+        <v>0.03150860238201618</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3549,6 +5153,18 @@
       <c r="F134">
         <v>-0.02167988944383036</v>
       </c>
+      <c r="G134">
+        <v>0.01758268244343955</v>
+      </c>
+      <c r="H134">
+        <v>-0.0561413137845766</v>
+      </c>
+      <c r="I134">
+        <v>0.01278153489691588</v>
+      </c>
+      <c r="J134">
+        <v>0.2175663856340783</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3572,6 +5188,18 @@
       <c r="F135">
         <v>-0.02166199020694988</v>
       </c>
+      <c r="G135">
+        <v>0.004335259924322107</v>
+      </c>
+      <c r="H135">
+        <v>-0.03015894352224104</v>
+      </c>
+      <c r="I135">
+        <v>-0.01316503689165871</v>
+      </c>
+      <c r="J135">
+        <v>5.831990050071042E-07</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3597,6 +5225,18 @@
       </c>
       <c r="F136">
         <v>-0.02093538399003252</v>
+      </c>
+      <c r="G136">
+        <v>0.003162006071009365</v>
+      </c>
+      <c r="H136">
+        <v>-0.02713280200810788</v>
+      </c>
+      <c r="I136">
+        <v>-0.01473796597195717</v>
+      </c>
+      <c r="J136">
+        <v>3.569741406078019E-11</v>
       </c>
     </row>
   </sheetData>
